--- a/public/Guia/7000-Recaudado-Renovacion-CuentasConceptos.xlsx
+++ b/public/Guia/7000-Recaudado-Renovacion-CuentasConceptos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SAC-IPE\public\Guia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\Guia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22D60A8-6148-4C6B-AD81-A7B4DA573A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F67BC56-90E9-45EF-B778-99F15BEE4BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>cuenta</t>
   </si>
@@ -97,6 +97,9 @@
   <si>
     <t xml:space="preserve">Por el recaudo de Ingresos por Venta de Bienes, Prestación de Servicios de Instituciones Públicas de Seguridad Social. (Préstamos con Renovación)
 </t>
+  </si>
+  <si>
+    <t>1.1.1.1.01.01</t>
   </si>
 </sst>
 </file>
@@ -481,7 +484,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="57.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="80.42578125" customWidth="1"/>
     <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -641,9 +644,18 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
